--- a/1_sinif/bahar/Lojistik_Yonetimi_Soru_Bankasi.xlsx
+++ b/1_sinif/bahar/Lojistik_Yonetimi_Soru_Bankasi.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,56 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001B5E3A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00065F46"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007A5800"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="009A3412"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00444444"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -82,48 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -580,7 +504,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>İsra Arrma Odaklı Lojisk Uygulamaları Örnek Teşkil Edecek Lojisk Uygulamaları başlığı alnda uygulamalar verilmişr. İsra arrma odaklı bir uygulama söz konusu değildir.</t>
+          <t>İsra Arrma Odaklı Lojisk Uygulamaları</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1075,7 +999,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Kâr en büyüklemesi Lojisk sistemlerin analizinde ve tasarımında kullanılan ve sayısal olarak tanımlanamayan nitel performans ölçütleri şu şekildedir:  Müşteri memnuniye: Müşteri memnuniyet seviyesi alınan ürün veya hizmetle belirlenir. Bu durum iç ve dış müşterilere uygulanabilir.  Esneklik: Lojisk sistemlerin talepteki dalgalanmalara verebileceği cevabın seviyesidir.  Bilgi ve malzeme akış entegrasyonu: Lojisk sistem içerisinde var olan tüm aşamaların arasındaki bilgi akışı ve malzeme taşınmasının entegrasyon seviyesidir.  Etkili risk yönemi: Lojisk sistemlerin hepsi birden fazla risk ögesi içerir. Etkili risk yönemi ise bu risklerin olasılığını veya etkisini en küçüklemenin seviyesi olarak tanımlanır.  Tedarikçi performansı: Hammaddelerin zamanında ve iyi koşullar alnda ürem firmalarına dağılma seviyesidir.</t>
+          <t>Kâr en büyüklemesi</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1165,7 +1089,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Araç doluluk oranı Teslimat Oranı (%)= Söz verilen tarihte (müşteri ile anlaşılan) Teslim Edilen Sipariş Sayısı/Toplam Sipariş Sayısı</t>
+          <t>Araç doluluk oranı</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1435,7 +1359,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Taşıma faaliyetlerinde kara yolu taşımacılığını mümkün olduğunca azaltan çözümler</t>
+          <t>Taşıma faaliyetlerinde kara yolu taşımacılığını mümkün</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1480,7 +1404,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>İşletmeden Devlet Kurum ve Kuruluşlarına E-Ticaret (B2C) İnternet kullanımının artması ile birlikte son kullanıcılar pek çok farklı kanaldan ürün veya hizmetlere ulaşabiliyor oldular. B2C e-caret hizme ülkemizde en çok tercih edilen e- caret türü olmakla birlikte aynı zamanda uluslararası kullanımıda son derece yaygındır. İnternet kullanımının artması ile birlikte son kullanıcılar farklı ülkelerdeki alışveriş kanallarını ziyaret edip, fiyat karşılaşrması yapıp kendileri için en uygun opsiyonu değerlendirmektedirler. B2C e-caret tarzında özellikle mal ve hizmetlerin sunumu sadece online kanallardan olacağı için ürünün ve hizmen son kullanıcıya detayları ile aktarılması yüksek adee saş gerçekleşmesi için önem arz etmektedir (Han, 2018). B2C’de fiyatlar ve ürünler açık ve net şekilde yayınlanır. Ürünün teslim koşulları, garan koşulları, fiya ve diğer özellikleri üreci veya sacı tarandan tek taraflı belirlenir ve tükecinin önüne sunulur. B2C'de tükeciler şahıs da olabilir perakendeci bir saş kanalı da.</t>
+          <t>İşletmeden Devlet Kurum ve Kuruluşlarına E-Ticaret</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1570,7 +1494,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>I, II, III ve IV taşımacılık, depolama, paketleme / ambalajlama, muayene gibi faaliyetlere ek olarak sipariş yönemi, stok yönemi, sigortalama ve gümrükleme fonksiyonlarını da için de barındırmaktadır. Bu faaliyetlerden içinde birçok açıdan en önemlisi taşımacılıkr. NAHTARI</t>
+          <t>I, II, III ve IV</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2515,7 +2439,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Ürünlerin bir araya gerildikleri ve ürem hana teslim edilmek üzere sıralandıkları bir merkez içerebilirler. üreciler, toptancılar ve perakendeciler adına saşa hazır ürünler depolar. Talepte beklenen arşlar/ azalışlar ve mevsimsellikler ile başa çıkmak için şirketlerin hazırlıklı olmalarını mümkün kılan bir tampon veya güvenlik stoku sağlarlar.</t>
+          <t>Ürünlerin bir araya gerildikleri ve ürem hana teslim</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2605,7 +2529,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Ağır yük vagonu (habis) vagon, yüksek kenarlı açık vagon, plaorm vagon, sarnıçlı vagon, ağır yük vagonu, özel vagon şeklinde sıralanabilir.</t>
+          <t>Ağır yük vagonu</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2740,7 +2664,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>İlgili tedarikçinin ölçeğinden, uzmanlığından yarım ve yaracılık gücünden yararlanmak</t>
+          <t>İlgili tedarikçinin ölçeğinden, uzmanlığından yarım ve</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2875,7 +2799,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Stok planlama ve kontrol sıralamak mümkündür:  Depolama  Ambalajlama ve Yükleme  Sanalma  Taşıma Yönemi  Geri Dönüşüm  Stok Planlama ve Kontrol  Talep Tahmini  Müşteri Hizmetleri  Sipariş Süreci  Diğer Hizmetler</t>
+          <t>Stok planlama ve kontrol</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3505,7 +3429,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Ortaklarla iş birliği yapabilmek operasyonlarında, bilgi teknolojisi kullanmanın AMAÇLARI şu şekilde sıralanabilir: • 1) Üremden teslimata veya san alma noktasına kadar, her ürün hakkında “bilgi toplamak” ve zincire kalan tüm taraflar için tam “görünürlük” sağlamak (Veri toplamak): Siparişler ve durumları hakkındaki veriler, verimli bir tedarik zincirini yönetmenin önemli bir parçasıdır. Buna bazen “izlenebilirlik” te denir. Bu aşamada ilerleyen bölümlerde anlalacak olan barkod, RFID, haa internet çözümlerinin yaygınlaşmasıyla IoT sistemleri, bu sürece katkı sağlamaktadır • 2) Bir sistemdeki gerekli bir veriye, “tek bir temas noktasından” erişebilmek (Veriye Erişmek): Tek bir veri temas veya veri giriş noktası, tekil veri girişi, tutarlılık sağlar. Çoğu şirkee Kurumsal Kaynak Planlama (ERP) sistemlerinin piyasaya sürülmesi, (çoğu şirken hâlâ tam olarak temiz veriye sahip olmamasına rağmen), bu sorunları büyük ölçüde çözmüştür. Firmalar arası veriye erişim ve veri transferinde EDI ile başlayan süreçte ark Blockchain teknolojisi konuşulmaktadır. Bu sayede hem saydamlık hem de güvenlik üst düzeyde olabilecekr. • 3) Faaliyet planlarını ve analizlerini, tüm tedarik zincirindeki enformasyona dayanarak “analiz” edebilmek (Veri analizi): Verileri analiz etme ihyacı, birçok sektördeki artan değişim hızı ve çeşitli sensörler ve internet üzerindeki faaliyetlerden (rakip fiyatlandırma gibi) elde edilen yeni veriler (genellikle büyük veri olarak adlandırılır) nedeniyle, daha da belirgin hâle gelmişr. Eskiden veri analizleri, ya hazır yazılımlarla ya da Excel çalışma sayfaları aracılığıyla yapılırdı ve BT departmanlarına bağımlılık söz konusuydu. “Analik çözümleri” sağlama ile ilgili, iki önemli gelişme olmuştur. İlk olarak, R ve Python gibi yeni dillerle makine öğreniminin (bazen yapay zekâ olarak adlandırılır) kullanımı artmışr ve güçlü içerikli yetenekler sağlamışr. İkincisi, Amazon Web Servisleri, Microso Azure ve diğer bulut sağlayıcıları aracılığıyla bulut bilişimin genişleme kolaylığıdır. Bu, büyük verilere, ucuz belleğe ve ölçeklenebilir bilgi işlem gücüne erişim sağlamaktadır ve bu nedenle büyük analik modelleri çalışrma imkânı doğmuştur. • 4) Tedarik zinciri ortaklarıyla, “işbirliği” yapabilmek (Ortaklarla ortak çalışmak): Tedarik zinciri işbirliğinde, Tedarikçi İlişkileri Yönemi (SRM) ve Müşteri İlişkileri Yönemi (CRM) gibi gelişmiş sistemler, işleri kolaylaşrır. Yukarıda belirğimiz gibi, “bulut hizmetler” şirketler arasında işbirliğini kolaylaşrmışr ve bunu destekleyen yazılımların kullanımı ve erişimi daha kolaylaşmışr</t>
+          <t>Ortaklarla iş birliği yapabilmek</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3820,7 +3744,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>İhracat beyannamesi CEVAP AN</t>
+          <t>İhracat beyannamesi</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3910,7 +3834,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Bilgisayar donanımları tutuldukça artabilir. Bunlara kaliteli şaraplar ve alkollü içkiler, purolar, değerli metaller ve taşlar, ankalar ve sanat eserleri örnek gösterilebilir. CEVAP AN</t>
+          <t>Bilgisayar donanımları</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4265,12 +4189,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Verimlilik Ölçümü, Verimlilik Değerlendirmesi, Verimlilik Gelişrmesi, Verimlilik Planlaması</t>
+          <t>Verimlilik Ölçümü, Verimlilik Değerlendirmesi, Verimlilik</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Verimlilik Ölçümü, Verimlilik Değerlendirmesi, Verimlilik Planlaması, Verimlilik Gelişrmesi</t>
+          <t>Verimlilik Ölçümü, Verimlilik Değerlendirmesi, Verimlilik</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4360,7 +4284,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Gerçek zamanlı veri işleme zamanlı veri işleme, bilgisayar sistemlerinin ve makinelerin verileri sürekli ve otomak olarak işleyebilme ve gerçek zamanlı veya yakın zamana ait çıklar ve öngörüler sunma yeteneklerini ifade eder (epicor, 2019).</t>
+          <t>Gerçek zamanlı veri işleme</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4540,7 +4464,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>25 ton ağırlık aşağıdaki tabloda gösterildiği gibidir. Tablo 4.1.Dingil Başına Düşen Maksimum Ağırlıklar Hat Kategorisi Maksimum Ağırlık A 16 ton B 18 ton C 20 ton D 22,5 ton E 25 ton</t>
+          <t>25 ton</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4585,7 +4509,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Bir depodaki günlük işlemleri kontrol etmeye ve yönetmeye yardımcı olan bir yazılım uygulamasıdır. bir depodaki günlük işlemleri kontrol etmeye ve yönetmeye yardımcı olan bir yazılım uygulamasıdır. Bir DYS yazılımı, stok tutma ve azaltmaya rehberlik eder, siparişlerin toplanmasını ve gönderilmesini opmize eder ve stok yenileme konusunda tavsiyelerde bulunur.</t>
+          <t>Bir depodaki günlük işlemleri kontrol etmeye ve yönetmeye</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4810,7 +4734,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Yeniden kullanım ve tamir dönen ürünün özelliğini tamamen kaybetmemiş sağlam parça/parçalarının benzer ya da aynı özellikteki başka ürünlerde kullanılmasıdır.</t>
+          <t>Yeniden kullanım ve tamir</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4990,7 +4914,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>II ve III sürdürülebilirliğe katkı sağladığı alanlardan birisi emisyonları azaltmak üzerinedir. Arrmak değildir.</t>
+          <t>II ve III</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5080,7 +5004,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>I, II ve III Programlama: Karar değişkenlerinin tümü kesikli değişken olduğu durumlardaki matemaksel modelleme türüdür. Bu yöntemlerin en bilenenleri; Dal-Sınır Algoritması, Sır-Bir Saklı Sayma Algoritmasıve Kesme Düzlemi Algoritması’dır.</t>
+          <t>I, II ve III</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5125,7 +5049,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>I, II ve IV amaçlara yönelik lojisk alanlar bulunmaktadır. Bu konuda bir terminoloji birliği sağlamak amacıyla söz konusu alanların faaliyet amaçlarına göre bir sınıflandırılması yapılmışr. Lojisk faaliyetlerle ilgili alanları; • Lojisk Merkezler, • Kentsel Aktarma Merkezleri, • Dış Ticaret Merkezleri, • Terminaller ve • Parklanma Alanları olarak beş temel sınıfa ayırabiliriz. NAHTARI</t>
+          <t>I, II ve IV</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5350,7 +5274,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Muayene ve gözem (transportaon) ve depolama (warehousing) ana faaliyetleri ile paketleme (packing), katma değerli hizmetler (value added services), gümrük (customs clearance), sipariş yönemi (order management / customer services), stok yönemi (inventory management), sigorta (insurance), muayene ve gözem (inspecon) tamamlayıcı faaliyetlerinden oluşan bir bütünleşik fonksiyondur (Şekil 1.1.). Lojisk, ürün/yükün çıkış ve varış noktaları arasındaki tüm malzeme hareketlerinin eşgüdümüdür.</t>
+          <t>Muayene ve gözem</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5440,7 +5364,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>tedarik ve girdi lojisği, teknoloji gelişrme, insan kaynakları yönemi, saş pazarlama</t>
+          <t>tedarik ve girdi lojisği, teknoloji gelişrme, insan kaynakları</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5485,7 +5409,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>İkincil Aktarma Merkezi büyük bir alana sahip, bölgesindeki tüm ülkelere yük gönderebilen ve alabilen, en az bir küresel ve bir ulusal ulaşrma koridoru üzerinde olan, tüm lojisk ve gümrük hizmetlerinin verildiği, içinde en az üç taşıma modu veya bu modlara etkin bağlanları ile en az iki intermodal terminali olan lojisk merkezdir</t>
+          <t>İkincil Aktarma Merkezi</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5530,7 +5454,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>İkincil Aktarma Merkezi büyük bir alana sahip, bölgesindeki tüm ülkelere yük gönderebilen ve alabilen, en az bir küresel ve bir ulusal ulaşrma koridoru üzerinde olan, tüm lojisk ve gümrük hizmetlerinin verildiği, içinde en az üç taşıma modu veya bu modlara etkin bağlanları ile en az iki intermodal terminali olan lojisk merkezdir</t>
+          <t>İkincil Aktarma Merkezi</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5845,7 +5769,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Kasırga iki tür riskten bahsetmek mümkündür. Bunlar iç riskler ve dış risklerdir. İç riskler; geç teslimatlar, fazla stok, kötü tahminler, finansal riskler, küçük kazalar, insan hatası, bilgi teknolojisi sistemindeki hatalar gibi normal operasyonlarda ortaya çıkan risklerdir. Dış riskler; deprem, kasırga, savaş gibi tedarik zinciri dışından kaynaklanan risklerdir. Örneğin, saldırılar, hastalık salgınları, fiyat arşları, caret ortaklarıyla ilgili sorunlar, hammadde sıkınsı, suç, finansal düzensizlikler v.b.</t>
+          <t>Kasırga</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5935,7 +5859,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Mavna otomobil vb. karayolu araçlarının kendi tekerlekleri üzerinde yüklenerek taşındığı gemilerdir.</t>
+          <t>Mavna</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6250,7 +6174,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Kabul kredili ödeme Against Good – Deferred Payment ) İthalatçının san aldığı malın bedelini, malı teslim aldıktan sonra yapılan sözleşmeye göre belirlenen tarihte ödeme yapmasını sağlayan ödeme yöntemidir.</t>
+          <t>Kabul kredili ödeme</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6340,7 +6264,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Uzun dönemli amaçların belirlenmesi sonra stratejik planların oluşturulmasının ilk aşaması işletmenin vizyon ve misyonun belirlenmesidir. Vizyon işletmenin uzun vadede, gelecekte ne yapması gerekğine dair bir görüş sağlar, o işlemenin gelecekte olmak istediği noktayı işaret etmektedir. Misyon ise işletmenin varlık nedenini, kendini nasıl bir işletme olarak gördüğünü, rekabet etmek istediği işletmeleri, hizmet sunmak istediği müşterilerini, ürünlerini tüm paydaşlarına anlağı bildirgedir. Misyonla işletmeler; “Ben kimim?”, “Ne üreyorum?”, “Kime ürem yapıyorum?”, “Değerlerim neler?” gibi soruların cevabını verirler.</t>
+          <t>Uzun dönemli amaçların belirlenmesi</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6385,7 +6309,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Sosyokültürel Çevre faaliyetlerini sürdürdüğü, ürem için girdilerini temin eği, üreği mal ve hizmetleri müşterilerine sağı ve kendi gibi benzer ürem yapan firmalar ile rekabet içinde bulunduğu çevredir.</t>
+          <t>Sosyokültürel Çevre</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">

--- a/1_sinif/bahar/Lojistik_Yonetimi_Soru_Bankasi.xlsx
+++ b/1_sinif/bahar/Lojistik_Yonetimi_Soru_Bankasi.xlsx
@@ -512,6 +512,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -557,6 +558,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -602,6 +604,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -647,6 +650,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -692,6 +696,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -737,6 +742,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -774,7 +780,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Standart Performans / Gerçekleşen (Fiili) Performans NAHTARI</t>
+          <t>Standart Performans / Gerçekleşen (Fiili) Performans</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -782,6 +788,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -827,6 +834,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -872,6 +880,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -917,6 +926,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -962,6 +972,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1007,6 +1018,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1044,7 +1056,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Doğru Ürün NAHTARI</t>
+          <t>Doğru Ürün</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1052,6 +1064,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1097,6 +1110,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1134,7 +1148,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>İç yönem amacı NAHTARI</t>
+          <t>İç yönem amacı</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1142,6 +1156,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1187,6 +1202,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1232,6 +1248,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1277,6 +1294,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1322,6 +1340,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1367,6 +1386,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1412,6 +1432,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1449,7 +1470,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Yalnız I CEVAP AN</t>
+          <t>Yalnız I</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1457,6 +1478,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1502,6 +1524,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1547,6 +1570,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1592,6 +1616,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1637,6 +1662,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1674,7 +1700,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Genek algoritma CEVAP AN</t>
+          <t>Genek algoritma</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1682,6 +1708,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1727,6 +1754,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1772,6 +1800,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1817,6 +1846,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1862,6 +1892,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1907,6 +1938,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1952,6 +1984,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1997,6 +2030,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2042,6 +2076,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2087,6 +2122,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2132,6 +2168,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2177,6 +2214,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2222,6 +2260,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2267,6 +2306,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2312,6 +2352,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2357,6 +2398,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2402,6 +2444,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2447,6 +2490,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2492,6 +2536,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2537,6 +2582,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2574,7 +2620,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tedarikçilere ve imalatçılara yakınlık CEVAP AN</t>
+          <t>Tedarikçilere ve imalatçılara yakınlık</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2582,6 +2628,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2627,6 +2674,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2672,6 +2720,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2717,6 +2766,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2762,6 +2812,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2807,6 +2858,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2852,6 +2904,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2897,6 +2950,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2942,6 +2996,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2987,6 +3042,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3032,6 +3088,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3077,6 +3134,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3122,6 +3180,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3167,6 +3226,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3212,6 +3272,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3257,6 +3318,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3302,6 +3364,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3347,6 +3410,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3392,6 +3456,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3437,6 +3502,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3482,6 +3548,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3527,6 +3594,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3572,6 +3640,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3617,6 +3686,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3654,7 +3724,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>İş sürekliliği CEVAP AN</t>
+          <t>İş sürekliliği</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3662,6 +3732,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3707,6 +3778,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3752,6 +3824,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3797,6 +3870,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3842,6 +3916,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3887,6 +3962,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3932,6 +4008,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3969,7 +4046,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Çalışanların Beklenleri NAHTARI</t>
+          <t>Çalışanların Beklenleri</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3977,6 +4054,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4022,6 +4100,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4067,6 +4146,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4112,6 +4192,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4157,6 +4238,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4202,6 +4284,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4247,6 +4330,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -4292,6 +4376,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -4337,6 +4422,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4382,6 +4468,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -4427,6 +4514,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -4472,6 +4560,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -4517,6 +4606,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4554,7 +4644,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Uzmanlık Seviyesi CEVAP AN</t>
+          <t>Uzmanlık Seviyesi</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4562,6 +4652,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -4607,6 +4698,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4652,6 +4744,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4697,6 +4790,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4742,6 +4836,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4787,6 +4882,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4832,6 +4928,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4877,6 +4974,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4922,6 +5020,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -4967,6 +5066,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -5012,6 +5112,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -5057,6 +5158,7 @@
           <t>E</t>
         </is>
       </c>
+      <c r="J103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -5094,7 +5196,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>I, III ve IV CEVAP AN</t>
+          <t>I, III ve IV</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5102,6 +5204,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -5147,6 +5250,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -5192,6 +5296,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -5237,6 +5342,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -5282,6 +5388,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -5327,6 +5434,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -5372,6 +5480,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -5417,6 +5526,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -5462,6 +5572,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -5499,7 +5610,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Farklılaşrma Stratejisi NAHTARI</t>
+          <t>Farklılaşrma Stratejisi</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5507,6 +5618,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -5552,6 +5664,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -5597,6 +5710,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -5642,6 +5756,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -5687,6 +5802,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -5732,6 +5848,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -5777,6 +5894,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -5822,6 +5940,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="J120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -5867,6 +5986,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -5912,6 +6032,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -5957,6 +6078,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -6002,6 +6124,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -6047,6 +6170,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -6092,6 +6216,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -6137,6 +6262,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="J127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -6182,6 +6308,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -6227,6 +6354,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -6272,6 +6400,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -6317,6 +6446,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="J131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -6354,7 +6484,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Yaygınlaşrma stratejileri NAHTARI</t>
+          <t>Yaygınlaşrma stratejileri</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6362,6 +6492,7 @@
           <t>D</t>
         </is>
       </c>
+      <c r="J132" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
